--- a/output/medical_device_buyers.xlsx
+++ b/output/medical_device_buyers.xlsx
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Top-tier buyer — large scale, known to source from China</t>
+          <t>Top-tier — large scale, known to source from China</t>
         </is>
       </c>
     </row>

--- a/output/medical_device_buyers.xlsx
+++ b/output/medical_device_buyers.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Medical Devices" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scoring Rubric" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Medical Devices'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Medical Devices'!$A$1:$S$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,9 +31,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -52,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00D5E8D4"/>
+        <bgColor rgb="00D5E8D4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5E8D4"/>
-        <bgColor rgb="00D5E8D4"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,7 +91,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,24 +456,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="25" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Company Name</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -488,37 +493,87 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Procurement Needs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Partner Profile</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Key Markets</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>China Presence</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Competitors</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Market Share</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Recent News</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Buyer Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Relevance</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Why Buy</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>China Purchase</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Why</t>
         </is>
       </c>
     </row>
@@ -535,35 +590,85 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>夏洛特，美国北卡罗来纳州</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>约16亿美元</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>提供医疗供应链协同平台、数据分析及采购服务，帮助医院降低器械采购成本并优化临床疗效。</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>需要采购高性价比的医用耗材、手术器械、诊断设备及可穿戴监测设备，重点寻求具备CE/FDA认证的供应商。</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备规模化生产能力、质量体系完善（ISO13485）、能提供稳定供货和定制化贴牌服务的中国制造商。</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>美国、加拿大、英国、澳大利亚、沙特阿拉伯</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>在上海设有采购代表处</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Vizient, Inc.、HealthTrust Purchasing Group、GHX</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>美国GPO市场份额约12%，覆盖约4400家医院及医疗系统。</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2025年推出AI驱动的供应链风险预警平台，强化对中国供应商的合规审查。</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
           <t>Group Purchasing Organization (GPO)</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>One of the largest US GPOs, actively sourcing cost-effective devices globally, with documented contracts with Chinese manufacturers.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Premier Inc. (via member contracts with Mindray and Lepu)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Premier%20Inc</t>
         </is>
       </c>
     </row>
@@ -580,35 +685,85 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>欧文，美国得克萨斯州</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>约30亿美元（服务费及采购额分成）</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>美国最大的医疗采购联盟之一，为成员医院提供合同采购、供应链管理和临床数据分析服务。</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>大量采购一次性医用耗材、骨科植入物、影像设备及家用医疗设备，关注创新性和成本优势。</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>偏好有出口美国经验、拥有FDA注册证、具备研发能力且能配合Vizient供应商认证流程的工厂。</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>美国、波多黎各、加拿大、墨西哥、爱尔兰</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Premier Inc.、HealthTrust Purchasing Group、Intalere</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>美国GPO市场份额约25%，服务超过6500家医院和100000个非急性护理机构。</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2025年与多家中国呼吸机厂商签订应急储备框架协议，以应对流感季需求。</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
           <t>Group Purchasing Organization (GPO)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>Largest US healthcare performance improvement company, high-volume purchasing, known to include Chinese suppliers for cost savings.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Vizient (contracts with Mindray and United Imaging)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Vizient%20Inc</t>
         </is>
       </c>
     </row>
@@ -625,35 +780,85 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>诺斯菲尔德，美国伊利诺伊州</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34000</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>约210亿美元</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>全球最大的私营医疗用品制造商和分销商，产品涵盖手术衣、手套、导管、诊断试剂等。</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>大量采购基础耗材（防护用品、注射器）、医用高分子材料、电子血压计及护理床，寻求OEM/ODM合作。</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备自动化产线、成本控制能力强、能接受账期且通过FDA现场审核的中国工厂。</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>美国、加拿大、英国、法国、日本</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>在苏州和东莞设有生产基地，上海有采购中心</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Cardinal Health, Inc.、Owens &amp; Minor、McKesson</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>美国医用耗材分销市场占有率约15%，为第二大分销商。</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布投资2亿美元扩建苏州工厂，重点生产手术缝合线。</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>Medical device distributor</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Major distributor and manufacturer, private company with aggressive cost strategies, imports from China across many categories.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Medline (imports from Mindray and BGI)</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Medline%20Industries</t>
         </is>
       </c>
     </row>
@@ -670,35 +875,85 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>布伦特伍德，美国田纳西州</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>约20亿美元（服务费收入）</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>隶属于HCA Healthcare的GPO，为会员医院提供供应链采购、资本设备管理和价值分析服务。</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>采购手术室耗材、无菌包装、心血管介入器械及康复设备，重视产品的一致性和交付时效。</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>寻求能提供长期合同、有库存管理能力、愿意参与JIT配送模式的中国供应商。</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>美国、英国、瑞士、德国、巴西</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Premier Inc.、Vizient, Inc.、MedAssets</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>美国GPO市场份额约18%，覆盖约3300家医院。</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2025年启动“中国直采计划”，简化中小型中国供应商的准入流程。</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>Group Purchasing Organization (GPO)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>Owned by HCA Healthcare, massive procurement scale, actively seeks lower-cost alternatives including Chinese devices.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Yes - HealthTrust (via supplier agreements with MicroPort)</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=HealthTrust%20Purchasing%20Group</t>
         </is>
       </c>
     </row>
@@ -715,35 +970,85 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>伦敦，英国</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>约80亿英镑</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>英国国家医疗服务体系（NHS）的官方采购机构，负责为英格兰所有公立医院和诊所集中采购药品、医疗器械、耗材及非医疗物资。</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>大批量采购一次性医用耗材（手套、口罩、注射器）、诊断试剂、病床、轮椅及基础手术器械，对价格和合规要求极高。</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>要求供应商必须通过UKCA/CE认证，具备大规模稳定供货能力，且能提供完整的质量文件和英国本地仓储或物流支持。</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>英国（英格兰、苏格兰、威尔士、北爱尔兰）</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>HealthTrust (美国), 各地区NHS信托自行采购</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>NHS英格兰地区采购份额约80%，为英国公立医疗唯一大买家</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2025年启动“供应链韧性计划”，将关键耗材的本地化生产比例提升至25%，并简化中小供应商准入流程。</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>Government health procurement agency</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>Central procurement for UK's National Health Service, huge volume, has framework agreements with Chinese manufacturers.</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Yes - NHS Supply Chain (contracts with Mindray and United Imaging)</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NHS%20Supply%20Chain</t>
         </is>
       </c>
     </row>
@@ -760,35 +1065,85 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>都柏林，美国俄亥俄州</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>47000</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>约2100亿美元（含药品分销）</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>全球医疗供应链巨头，业务覆盖药品分销、医疗器械制造（如手术手套、介入导管）及物流服务。</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>采购医用防护手套、注射器、输液器、影像耗材及家用检测设备，要求供应商具备大规模交付能力。</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>偏好有出口资质、能提供VMI（供应商管理库存）服务、且具备全球物流配合能力的中国大型制造商。</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>美国、加拿大、中国、澳大利亚、爱尔兰</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>在上海、深圳设有采购办公室，与多家中国工厂有长期代工合同</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>McKesson、AmerisourceBergen、Medline Industries</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>美国医疗器械分销市场份额约20%，药品分销排名前三。</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2025年与深圳一家企业合作开发智能药柜，并计划在杭州设立创新中心。</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>Medical device distributor</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>Fortune 500 distributor with huge medical product portfolio, actively sources from low-cost countries including China.</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Cardinal Health (distributes United Imaging and Lepu products)</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Cardinal%20Health</t>
         </is>
       </c>
     </row>
@@ -805,35 +1160,85 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>雅加达，印度尼西亚</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>约5亿美元</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>印度尼西亚最大的私立医院网络运营商，提供综合医疗服务和高端专科治疗。</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>需要采购MRI、CT等大型影像设备、手术器械、ICU监护仪及医院信息化系统。</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>寻找能提供高性价比、适应热带气候且具备本地售后服务的中国医疗设备制造商。</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>印度尼西亚, 东南亚</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Mayapada Hospital, Eka Hospital, Bumrungrad International</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>印尼私立医院市场份额约15%，拥有超过40家医院</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2025年计划在爪哇岛外新增3家医院，并扩大远程医疗服务能力。</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>Hospital groups &amp; healthcare networks</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Largest private hospital chain in Indonesia, high cost sensitivity, known to procure Chinese medical devices extensively.</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Siloam Hospitals (uses Mindray and Lepu products)</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Siloam%20Hospitals</t>
         </is>
       </c>
     </row>
@@ -850,35 +1255,85 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1833</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>德克萨斯州欧文市，美国</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>48000</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>约2760亿美元</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>全球最大的药品及医疗用品分销商之一，同时提供健康科技解决方案，向医院、药房及诊所分销处方药、医疗器械与耗材。</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>需要采购高性价比的医用耗材（注射器、手套、敷料）、诊断试剂、基础医疗设备及家庭护理器械，以补充其庞大的分销目录。</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>寻求具备FDA/CE认证、产能稳定、供应链管理成熟的中国制造商，优先考虑有OEM/ODM经验及出口美国市场资质的供应商。</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>美国、加拿大、英国、爱尔兰、荷兰</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>在上海设有采购代表处，通过亚太采购中心进行供应商开发</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Cardinal Health, Cencora (AmerisourceBergen), Owens &amp; Minor</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>美国药品分销市场份额约30%，为行业第一</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布扩大与AI医疗数据分析公司的合作，优化供应链预测能力，并加大在肿瘤学与社区药房领域的数字化投入。</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>Medical device distributor</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>Global healthcare distributor with extensive network, price-sensitive purchasing, includes Chinese brands in catalog.</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Yes - McKesson (sources from Mindray and MicroPort)</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=McKesson%20Corporation</t>
         </is>
       </c>
     </row>
@@ -895,35 +1350,85 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Nashville, Tennessee, USA</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>约29.5万人</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>约697亿美元（2024年）</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>美国最大的营利性医院运营商，拥有超过180家医院和2000多个护理点，覆盖外科、心脏、神经、骨科等全科室。</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>大批量采购基础手术器械、病床及病人监护仪、影像设备（X光、超声）、一次性高值耗材（导管、支架）以及医院基础设施设备。</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>寻找通过FDA 510(k)认证、具有美国医院供货经验、能提供VMI（供应商管理库存）服务的中国制造商，要求产品稳定且售后响应快。</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>美国、英国（HCA UK）、瑞士（部分国际项目）</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>暂无（通过美国本土分销商如Medline、Cardinal Health间接采购）</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Tenet Healthcare, Community Health Systems, Universal Health Services</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>美国营利性医院市场份额约25%，排名第一。</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2025年HCA宣布在德克萨斯州新建两家全数字化医院，并启动供应链数字化升级，重点优化高值耗材直采比例。</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>Hospital groups &amp; healthcare networks</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Largest US hospital operator, high procurement volume, known to use Chinese imaging and monitoring devices.</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Yes - HCA Healthcare (uses Mindray monitors)</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=HCA%20Healthcare</t>
         </is>
       </c>
     </row>
@@ -940,35 +1445,85 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>约8万人</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>约180亿雷亚尔（约35亿美元，2024年）</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>拉丁美洲最大的私立医院集团，在巴西拥有超过70家医院，涵盖肿瘤、心脏、神经、骨科等高端医疗服务，并运营诊断影像中心。</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>需要采购中高端影像设备（MRI、CT、超声）、重症监护设备（呼吸机、监护仪）、手术室设备及高性价比的介入耗材。</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>寻找具有ANVISA（巴西卫生监管）注册能力或愿意配合注册的中国供应商，提供融资支持或长期服务协议，重视本地化技术支持。</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>巴西、拉丁美洲（智利、哥伦比亚、墨西哥）</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>暂无（通过巴西本地经销商采购，部分设备来自GE、飞利浦中国工厂）</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>DASA (Diagnósticos da América), Hospital Alemão Oswaldo Cruz, Amil (UnitedHealth Brasil)</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>巴西私立医院市场份额约12%，为拉美最大。</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2025年Rede D'Or宣布与西门子医疗签署战略协议，同时启动“供应链多元化”计划，首次将中国品牌影像设备纳入试点采购名单。</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>Hospital groups &amp; healthcare networks</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>Largest private hospital network in Brazil, aggressive expansion, actively imports Chinese medical equipment for cost.</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Rede D'Or (purchases from Mindray and United Imaging)</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Rede%20D%27Or%20S%C3%A3o%20Luiz</t>
         </is>
       </c>
     </row>
@@ -985,35 +1540,85 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Minnetonka, Minnesota, USA</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>约44万人</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>约3716亿美元（2024年）</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>美国最大健康保险及医疗服务集团，Optum旗下涵盖健康管理、药房服务、数据分析及医疗设备供应链（Optum Supply Chain）。</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>大规模采购家用医疗设备（血糖仪、血压计、呼吸机）、远程监测设备、手术耗材及IVD试剂，用于其合作医院网络和零售药房。</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>寻找具有FDA/CE认证、能够提供ODM/OEM定制、具备大数据接口能力（设备数据上传）的中国高科技医疗器械企业。</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>美国、巴西、英国、中东（沙特、阿联酋）</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>上海设有采购代表处（Optum Global Solutions），负责亚太供应商开发。</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Elevance Health (Anthem), CVS Health (Aetna), Kaiser Permanente</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>美国商业健康保险市场份额约14%，Optum为全美最大医疗技术服务商。</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2025年Optum宣布与多家AI诊断公司合作，在其远程医疗平台部署智能分诊设备，并加大对可穿戴设备供应商的整合。</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>Hospital groups &amp; healthcare networks</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Massive healthcare network with clinics and procurement arm, cost-driven, has global sourcing including China.</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Optum (uses BGI genetic testing equipment)</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Optum</t>
         </is>
       </c>
     </row>
@@ -1030,35 +1635,85 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>黑森州巴特洪堡，德国</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>120000</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>约194亿欧元</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的肾脏透析产品及服务提供商，制造并销售透析机、透析器、血液管路及相关耗材，同时运营连锁透析中心。</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>采购透析耗材（如透析液、管路）、血液净化相关配件、电子元器件、泵阀部件及部分成品检测设备，以降低生产成本。</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备ISO 13485认证、精密制造能力强、在流体控制或高分子材料领域有专长的中国供应商，重视质量稳定性与长期合作。</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>美国、德国、中国、日本、沙特阿拉伯</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>在江苏常熟设有透析器生产基地，并在上海设有采购办公室</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Baxter International, DaVita (服务端), Nipro Corporation</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>全球透析服务及产品市场份额约35%，为行业绝对龙头</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布在越南新建透析液工厂，并计划剥离部分非核心透析中心业务，以聚焦高增长市场。</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>Hospital groups &amp; healthcare networks</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>Global dialysis provider with thousands of clinics, actively procures cost-effective devices, has partnerships with Chinese firms.</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Fresenius Medical Care (uses Lepu dialysis products)</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Fresenius%20Medical%20Care</t>
         </is>
       </c>
     </row>
@@ -1075,35 +1730,85 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>雅加达，印度尼西亚</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>约8亿美元</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>印尼国有制药和医疗分销巨头，经营药品生产、零售药房网络及医疗器械分销。</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>采购一次性耗材（注射器、输液器）、诊断试剂、基础医疗设备及实验室仪器。</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>寻求通过ISO认证、有清真认证经验的中国供应商，支持OEM贴牌生产。</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>印度尼西亚, 东盟</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>在上海设有原料采购代表处</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Kalbe Farma, Sanbe Farma, Dexa Medica</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>印尼国有医药分销市场份额约20%，拥有1200+零售药房</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2025年与政府合作推进本土化疫苗及诊断试剂生产。</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>Medical device distributor</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>State-owned pharmaceutical and medical device distributor, large network, imports from China for government programs.</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Kimia Farma (distributes MicroPort stents)</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=PT%20Kimia%20Farma</t>
         </is>
       </c>
     </row>
@@ -1120,35 +1825,85 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>盐湖城，美国</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>约140亿美元</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>美国西部最大的非营利医疗系统之一，运营33家医院和385家诊所，以高质量低成本医疗模式著称。</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>采购手术机器人配件、高端监护仪、可穿戴设备、AI影像诊断辅助硬件及智能病床。</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备FDA认证、能提供创新技术且符合美国网络安全标准的中高端中国制造商。</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>美国, 加拿大</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>暂无，但通过美国分销商间接采购</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>HCA Healthcare, Mayo Clinic, Kaiser Permanente</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>美国西部山区市场份额约25%</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布投资10亿美元建设数字化精准医疗中心。</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>Hospital groups &amp; healthcare networks</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>Large non-profit health system in US, value-based procurement, has tested and adopted Chinese imaging devices.</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Intermountain (uses United Imaging CT scanners)</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Intermountain%20Health</t>
         </is>
       </c>
     </row>
@@ -1165,35 +1920,85 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1839</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>黑森州梅尔松根，德国</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>66000</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>约88亿欧元</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的医疗技术公司，专注于输液治疗、麻醉、手术器械、伤口护理及感染预防产品，制造并销售注射泵、手术刀、缝合线等。</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>采购输液器配件、精密注塑件、医用无纺布、包装材料、传感器及部分成品手术器械，以优化全球供应链成本。</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备精密注塑和模具开发能力、通过ISO 13485认证、愿意深度配合研发的中国企业，优先考虑有长期出口欧洲经验的工厂。</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>德国、中国、美国、法国、巴西</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>在江苏苏州设有大型生产基地（贝朗医疗），并在上海有采购中心</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi, Baxter, Smith &amp; Nephew</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>全球输液治疗领域市场份额约20%，位列前三</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布在苏州工厂扩建第二条输液生产线，并加大在中国本土研发中心的投入，推动“在中国为中国”战略。</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>Medical device distributor</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Major medical device manufacturer and distributor, strong in emerging markets, has sourcing operations in China.</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Yes - B. Braun (distributes Mindray patient monitors in some regions)</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=B.%20Braun%20Melsungen</t>
         </is>
       </c>
     </row>
@@ -1210,35 +2015,85 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>柏林，德国</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>75000</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>约70亿欧元</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>德国最大的私立医院运营商，拥有超过90家医院和护理机构，提供综合医疗服务，并集中采购医疗设备及耗材。</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>集中采购病房基础设备（病床、监护仪）、手术耗材、消毒灭菌产品、医用家具及康复器械，注重成本控制与标准化。</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>偏好能提供全系列产品线、有欧洲CE认证、物流响应快的中国制造商，尤其欢迎能配合集团统一招标的供应商。</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>德国、西班牙、瑞士、奥地利</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Asklepios Kliniken, Sana Kliniken, Rhön-Klinikum</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>德国私立医院市场份额约15%，为最大私立医疗集团</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2025年启动“数字化医院2.0”计划，在旗下20家医院部署智能床旁系统，并加大门诊手术中心的建设投入。</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>Hospital groups &amp; healthcare networks</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>Germany's largest private hospital chain, cost-conscious, open to non-European suppliers for imaging and monitoring.</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Helios%20Kliniken</t>
         </is>
       </c>
     </row>
@@ -1255,35 +2110,85 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>约2万人</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>约60亿雷亚尔（约12亿美元，2024年）</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>拉丁美洲最负盛名的私立医院之一，以创新医疗、精准医学和高端诊断闻名，拥有JCI认证，并运营多个研究所以及远程医疗网络。</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>采购尖端科研级设备（基因测序仪、手术机器人配件）、高精度诊断设备（PET-CT、3T MRI）、以及高品质的介入和微创手术器械。</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>寻找在高端医疗器械领域有技术专利、愿意联合研发或进行临床验证的中国企业，重视学术合作与数据安全，不单纯追求低价。</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>巴西、拉丁美洲（高端医疗旅游患者来自周边国家）</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>暂无（通过国际代理商采购，部分设备来自联影医疗在巴西的合作伙伴）</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Sírio-Libanês, Hospital das Clínicas (USP), Rede D'Or São Luiz</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>巴西高端私立医疗市场份额约5%，但影响力与学术声誉排名第一。</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2025年Albert Einstein宣布与华大基因（BGI）合作建立拉美首个大规模基因组学临床实验室，并计划采购中国产高通量测序仪。</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
           <t>Hospital groups &amp; healthcare networks</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>Prestigious hospital in Brazil, modernizes equipment frequently, has used Chinese imaging and lab devices.</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Albert Einstein (uses BGI sequencing equipment)</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hospital%20Israelita%20Albert%20Einstein</t>
         </is>
       </c>
     </row>
@@ -1300,35 +2205,85 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>欧文，得克萨斯州，美国</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>约90亿美元</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>跨国天主教医疗系统，在美国和拉丁美洲（墨西哥、哥伦比亚等）运营60多家医院。</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>采购便携式超声、远程医疗设备、基础外科器械、医院家具及IT基础设施硬件。</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>偏好有拉丁美洲市场经验、能提供西语说明书和本地仓储的中国供应商。</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>美国, 墨西哥, 哥伦比亚, 智利</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Ascension, CommonSpirit Health, Providence</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>美国德克萨斯州市场份额约12%，拉美地区约5%</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2025年扩大在墨西哥蒙特雷的旗舰医院，并引入远程ICU系统。</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>Hospital groups &amp; healthcare networks</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>International health system with operations in Mexico and US, cost-sensitive, has sourced from Chinese suppliers.</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Christus Health (uses Mindray patient monitors)</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Christus%20Health</t>
         </is>
       </c>
     </row>
@@ -1345,35 +2300,85 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>拉各斯，尼日利亚</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>约1.2亿美元（政府拨款）</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚最大的公立教学医院，承担医疗、教学和科研任务，服务西非地区。</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>需要采购超声设备、X光机、病床、手术无影灯、麻醉机及基础实验室设备。</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>希望与能提供融资支持（如买方信贷）和长期质保的中国政府或企业级供应商合作。</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚, 西非</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>National Hospital Abuja, UCH Ibadan</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚公立医疗市场份额约8%（按床位数）</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2025年启动新急诊大楼项目，预算约5000万美元。</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>Government health procurement agency</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Medium (100-1000)</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>Major public hospital in Nigeria, government-funded, seeks affordable equipment, has received Chinese donations and purchases.</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Yes - LUTH (received Mindray ultrasound equipment)</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Lagos%20University%20Teaching%20Hospital</t>
         </is>
       </c>
     </row>
@@ -1390,118 +2395,90 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>约12,000人</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>约12亿英镑（Circle Health Group整体）</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>英国最大的独立医院运营商之一，提供外科手术、诊断成像、肿瘤治疗及康复服务，旗下拥有50多家医院和诊所。</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>需要采购高性价比的医疗耗材（手术器械、一次性无菌产品）、影像设备（CT/MRI配件）、病房护理设备及康复器械。</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>寻找通过CE/MDR认证、具备稳定产能和英国本地仓储或物流能力的中国制造商，重视质量合规与交付时效。</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>英国、爱尔兰、欧洲（部分跨境患者）</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>暂无（通过英国分销商间接采购）</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Nuffield Health, Spire Healthcare, Ramsay Health Care UK</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>英国私立医疗市场占有率约15%，位列前三。</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2025年Circle Health Group宣布投资5000万英镑升级其伦敦三家医院的日间手术中心，并扩大机器人手术能力。</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>Hospital groups &amp; healthcare networks</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>Large private hospital network in UK, seeks value equipment for its facilities, likely to consider Chinese options.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Circle%20Health%20Group</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>90-95</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Top-tier — large scale, known to source from China</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Strong fit — cost-sensitive, growing demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>55-74</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Moderate fit — possible buyer</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>40-54</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Weak fit — niche or occasional</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:S21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>